--- a/结果/题型分析报告.xlsx
+++ b/结果/题型分析报告.xlsx
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>难度(平均得分率)</t>
+          <t>平均得分</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -461,13 +461,13 @@
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.713</v>
+        <v>7.133</v>
       </c>
       <c r="E2" t="n">
         <v>0.713</v>
       </c>
       <c r="F2" t="n">
-        <v>0.771</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="3">
@@ -483,13 +483,13 @@
         <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.727</v>
+        <v>14.533</v>
       </c>
       <c r="E3" t="n">
         <v>0.727</v>
       </c>
       <c r="F3" t="n">
-        <v>0.856</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="4">
@@ -505,13 +505,13 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.735</v>
+        <v>4.411</v>
       </c>
       <c r="E4" t="n">
         <v>0.735</v>
       </c>
       <c r="F4" t="n">
-        <v>0.636</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="5">
@@ -527,13 +527,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.608</v>
+        <v>2.433</v>
       </c>
       <c r="E5" t="n">
         <v>0.608</v>
       </c>
       <c r="F5" t="n">
-        <v>0.679</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="6">
@@ -549,13 +549,13 @@
         <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>0.711</v>
+        <v>10.672</v>
       </c>
       <c r="E6" t="n">
         <v>0.711</v>
       </c>
       <c r="F6" t="n">
-        <v>0.754</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="7">
@@ -571,13 +571,13 @@
         <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>0.779</v>
+        <v>19.472</v>
       </c>
       <c r="E7" t="n">
         <v>0.779</v>
       </c>
       <c r="F7" t="n">
-        <v>0.718</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="8">
@@ -593,13 +593,13 @@
         <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>0.652</v>
+        <v>13.039</v>
       </c>
       <c r="E8" t="n">
         <v>0.652</v>
       </c>
       <c r="F8" t="n">
-        <v>0.742</v>
+        <v>0.211</v>
       </c>
     </row>
   </sheetData>
